--- a/results/mummichog/BC_vs_PC/tables/mcg_pathwayanalysis_BC_vs_PC.xlsx
+++ b/results/mummichog/BC_vs_PC/tables/mcg_pathwayanalysis_BC_vs_PC.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="233">
   <si>
     <t>pathway</t>
   </si>
@@ -40,91 +40,445 @@
     <t>C21-steroid hormone biosynthesis and metabolism</t>
   </si>
   <si>
-    <t>E2377,E627,E187,E612,E94,E997,E613,E95,E12,E302,E1285,E1065,E57,E958,E1286,E959,E1543,E59,E886,E105,E1301,E1182,E2463,E1686,E887,E2589,E1183,E1546,E1709,E1640,E184,E331,E1394,E625,E186</t>
-  </si>
-  <si>
-    <t>C05301/hestratriol/C05141/CE2179,C05489/C05471/C05474,C03917/C05293/C00523/C04373/C04295,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,CE2211/C05480,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,C18038/C05138/C04518/C05485,C18045/C14497/C18075/C05294/C05139,dhea/C03772/C01227/C00674/C00535,C05490,C05488/C05497/C05477/C02140,C04042/C01953/C03681,dhea/C03772/C01227/C00674/C00535,C04042/C01953/C03681,CE2186/CE2183/C05302/C05284/C05290/C05140,C05488/C05497/C05477/C02140,17ahprgstrn/C03205/C05498/C01176,C05472,C05504,C00410,andrstndn/C00280,C00762/C01780,17ahprgstrn/C03205/C05498/C01176,C00468,C00410,CE2186/CE2183/C05302/C05284/C05290/C05140,C00951,C01124/C05469/C00735/C05473,C03917/C05293/C00523/C04373/C04295,C05487/C05475/C05478,C05476,C05489/C05471/C05474,C03917/C05293/C00523/C04373/C04295</t>
-  </si>
-  <si>
-    <t>2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$allopregnanolone/3alpha-Hydroxy-5beta-pregnane-20-one$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$/17alpha-Hydroxypregnenolone/17alpha,20alpha-Dihydroxypregn-4-en-3-one/21-Hydroxypregnenolone$/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$11-Dehydrocorticosterone$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$4-methoxy-17beta-estradiol/2-hydroxy-3-methoxy-17beta-estradiol/2-Methoxyestradiol-17beta/11beta-Hydroxyandrost-4-ene-3,17-dione; Androst-4-ene-3,17-dione-11beta-ol; 4-Androsten-11beta-ol-3,17-dione/19-Hydroxyandrost-4-ene-3,17-dione; 19-Hydroxyandrostenedione/16alpha-Hydroxyandrost-4-ene-3,17-dione; 4-Androsten-16alpha-ol-3,17-dione$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$16-Glucuronide-estriol; 16alpha,17beta-Estriol 16-(beta-D-glucuronide)$Progesterone; 4-Pregnene-3,20-dione$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$Cortisone; 17alpha,21-Dihydroxy-4-pregnene-3,11,20-trione; Kendall's compound E; Reichstein's substance Fa/Aldosterone; 11beta,21-Dihydroxy-3,20-dioxo-4-pregnen-18-al$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$Estrone; 3-Hydroxy-1,3,5(10)-estratrien-17-one$Progesterone; 4-Pregnene-3,20-dione$4-methoxy-17beta-estradiol/2-hydroxy-3-methoxy-17beta-estradiol/2-Methoxyestradiol-17beta/11beta-Hydroxyandrost-4-ene-3,17-dione; Androst-4-ene-3,17-dione-11beta-ol; 4-Androsten-11beta-ol-3,17-dione/19-Hydroxyandrost-4-ene-3,17-dione; 19-Hydroxyandrostenedione/16alpha-Hydroxyandrost-4-ene-3,17-dione; 4-Androsten-16alpha-ol-3,17-dione$Estradiol-17beta; beta-Estradiol; Estradiol$18-Hydroxycorticosterone/17alpha,21-Dihydroxy-5beta-pregnane-3,11,20-trione; 5beta-Pregnane-17alpha,21-diol-3,11,20-trione; 4,5beta-Dihydrocortisone/Cortisol; Hydrocortisone; 11beta,17alpha,21-Trihydroxy-4-pregnene-3,20-dione; Kendall's compound F; Reichstein's substance M/11beta,21-Dihydroxy-3,20-oxo-5beta-pregnan-18-al$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Tetrahydrocorticosterone$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol</t>
+    <t>E1278,E1293,E957,E101,E958,E1174,E1538,E12,E90,E1175,E326,E620,E885,E91,E607,E1386,E622,E608,E182,E624,E297,E990,E626,E1277,E1535</t>
+  </si>
+  <si>
+    <t>dhea/C03772/C01227/C00674/C00535,C05504,C04042/C01953/C03681,C05472,C04042/C01953/C03681,C00410,CE2186/CE2183/C05302/C05284/C05290/C05140,C18038/C05138/C04518/C05485,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,C00410,C05487/C05475/C05478,C05488/C05497/C05477/C02140,17ahprgstrn/C03205/C05498/C01176,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,C11134/tststeroneglc,C05476,C05488/C05497/C05477/C02140,C11134/tststeroneglc,C03917/C05293/C00523/C04373/C04295,C05489/C05471/C05474,C18045/C14497/C18075/C05294/C05139,CE2211/C05480,C05489/C05471/C05474,dhea/C03772/C01227/C00674/C00535,CE2186/CE2183/C05302/C05284/C05290/C05140</t>
+  </si>
+  <si>
+    <t>Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$16-Glucuronide-estriol; 16alpha,17beta-Estriol 16-(beta-D-glucuronide)$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Progesterone; 4-Pregnene-3,20-dione$4-methoxy-17beta-estradiol/2-hydroxy-3-methoxy-17beta-estradiol/2-Methoxyestradiol-17beta/11beta-Hydroxyandrost-4-ene-3,17-dione; Androst-4-ene-3,17-dione-11beta-ol; 4-Androsten-11beta-ol-3,17-dione/19-Hydroxyandrost-4-ene-3,17-dione; 19-Hydroxyandrostenedione/16alpha-Hydroxyandrost-4-ene-3,17-dione; 4-Androsten-16alpha-ol-3,17-dione$/17alpha-Hydroxypregnenolone/17alpha,20alpha-Dihydroxypregn-4-en-3-one/21-Hydroxypregnenolone$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Progesterone; 4-Pregnene-3,20-dione$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$Tetrahydrocorticosterone$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al$/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$allopregnanolone/3alpha-Hydroxy-5beta-pregnane-20-one$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$4-methoxy-17beta-estradiol/2-hydroxy-3-methoxy-17beta-estradiol/2-Methoxyestradiol-17beta/11beta-Hydroxyandrost-4-ene-3,17-dione; Androst-4-ene-3,17-dione-11beta-ol; 4-Androsten-11beta-ol-3,17-dione/19-Hydroxyandrost-4-ene-3,17-dione; 19-Hydroxyandrostenedione/16alpha-Hydroxyandrost-4-ene-3,17-dione; 4-Androsten-16alpha-ol-3,17-dione</t>
+  </si>
+  <si>
+    <t>Arachidonic acid metabolism</t>
+  </si>
+  <si>
+    <t>E484,E1237,E195,E1224,E897,E210,E193,E196,E267</t>
+  </si>
+  <si>
+    <t>C06426/C06427,CE2567/CE2566/CE5178/CE4990/CE4876/CE5304/CE5349/CE6508/CE7080/CE7091/CE7097/CE7084/CE7083,C00909,CE6248/CE6247/CE2569/CE2568/CE5662,C00219,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,C00909,C00909,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781</t>
+  </si>
+  <si>
+    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$5(S),6(S)-epoxy-15(S)-hydroxy-7E,9E,11Z,13E-eicosatetraenoic acid anion/5(S),6(S)-epoxy-15(R)-hydroxyeicosatetraenoate/5-oxo-6-trans-leukotriene B4/12-oxo-leukotriene B4/delta12-Prostaglandin J2//5-oxo-6E-12-epi-LTB4/5-hydroperoxy-EPA/15(S)-hydroperoxy-EPE/15(R)-hydroperoxy-EPE/5-oxo-12(S)-hydroxy-eicosa-6E,8Z,10E,14Z-tetraenoate//leukotriene B5$Leukotriene A4$20-OH-hepoxilin A3/5,12,20-TriHETE/15-epi-lipoxin B4/15-epi-lipoxin A4/13,14-dihydro-15-oxo-lipoxin A4$arachidonic acid$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$Leukotriene A4$Leukotriene A4$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid</t>
+  </si>
+  <si>
+    <t>Androgen and estrogen biosynthesis and metabolism</t>
+  </si>
+  <si>
+    <t>E12,E90,E608,E1278,E1293,E1764,E91,E182,E1277,E957,E425,E607,E958,E1535,E1538,E297</t>
+  </si>
+  <si>
+    <t>C18038/C05138/C04518/C05485,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,C11134/tststeroneglc,dhea/C03772/C01227/C00674/C00535,C05504,C11131,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,C03917/C05293/C00523/C04373/C04295,dhea/C03772/C01227/C00674/C00535,C04042/C01953/C03681,CE2209,C11134/tststeroneglc,C04042/C01953/C03681,CE2186/CE2183/C05302/C05284/C05290/C05140,CE2186/CE2183/C05302/C05284/C05290/C05140,C18045/C14497/C18075/C05294/C05139</t>
+  </si>
+  <si>
+    <t>/17alpha-Hydroxypregnenolone/17alpha,20alpha-Dihydroxypregn-4-en-3-one/21-Hydroxypregnenolone$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$16-Glucuronide-estriol; 16alpha,17beta-Estriol 16-(beta-D-glucuronide)$2-Methoxy-estradiol-17beta 3-glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$5alpha-androstane-3alpha,17beta-diol$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$4-methoxy-17beta-estradiol/2-hydroxy-3-methoxy-17beta-estradiol/2-Methoxyestradiol-17beta/11beta-Hydroxyandrost-4-ene-3,17-dione; Androst-4-ene-3,17-dione-11beta-ol; 4-Androsten-11beta-ol-3,17-dione/19-Hydroxyandrost-4-ene-3,17-dione; 19-Hydroxyandrostenedione/16alpha-Hydroxyandrost-4-ene-3,17-dione; 4-Androsten-16alpha-ol-3,17-dione$4-methoxy-17beta-estradiol/2-hydroxy-3-methoxy-17beta-estradiol/2-Methoxyestradiol-17beta/11beta-Hydroxyandrost-4-ene-3,17-dione; Androst-4-ene-3,17-dione-11beta-ol; 4-Androsten-11beta-ol-3,17-dione/19-Hydroxyandrost-4-ene-3,17-dione; 19-Hydroxyandrostenedione/16alpha-Hydroxyandrost-4-ene-3,17-dione; 4-Androsten-16alpha-ol-3,17-dione$/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one</t>
+  </si>
+  <si>
+    <t>De novo fatty acid biosynthesis</t>
+  </si>
+  <si>
+    <t>E78,E484,E897,E912</t>
+  </si>
+  <si>
+    <t>CE5932/C02075/C06428/CE5013,C06426/C06427,C00219,C00712</t>
+  </si>
+  <si>
+    <t>13,14-epoxy-retinol/Retinyl ester; all-trans-Retinyl ester/(5Z,8Z,11Z,14Z,17Z)-Icosapentaenoic acid; (5Z,8Z,11Z,14Z,17Z)-Eicosapentaenoic acid; Eicosapentaenoic acid; 5,8,11,14,17-Icosapentaenoic acid; (5Z,8Z,11Z,14Z,17Z)-Eicosapentaenoate/$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$arachidonic acid$(9Z)-Octadecenoic acid; (Z)-Octadec-9-enoic acid; Oleate; Oleic acid</t>
+  </si>
+  <si>
+    <t>Linoleate metabolism</t>
+  </si>
+  <si>
+    <t>E1910,E316,E1669,E484,E646,E2121,E1380,E317,E762,E1891,E1378,E302,E2546,E303</t>
+  </si>
+  <si>
+    <t>CE2577,C04717/C14827,C08261,C06426/C06427,CE6415/CE6502,CE2576,C14762/C14826/C14825,C04717/C14827,CE2061,CE5528,C14762/C14826/C14825,CE5526/CE5527/C14765,CE2006/CE6506,CE5526/CE5527/C14765</t>
+  </si>
+  <si>
+    <t>$(9Z,11E)-(13S)-13-Hydroperoxyoctadeca-9,11-dienoic acid; (9Z,11E)-(13S)-13-Hydroperoxyoctadeca-9,11-dienoate; 13(S)-HPODE; 13S-Hydroperoxy-9Z,11E-octadecadienoic acid/9(S)-HPODE; 9(S)-HPOD; (10E,12Z)-(9S)-9-Hydroperoxyoctadeca-10,12-dienoic acid$$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$/$$13(S)-HODE; (13S)-Hydroxyoctadecadienoic acid; (9Z, 11E)-(13S)-13-Hydroxyoctadeca-9,11-dienoic acid/12(13)-EpOME; (12R,13S)-(9Z)-12,13-Epoxyoctadecenoic acid/9(10)-EpOME; (9R,10S)-(12Z)-9,10-Epoxyoctadecenoic acid$(9Z,11E)-(13S)-13-Hydroperoxyoctadeca-9,11-dienoic acid; (9Z,11E)-(13S)-13-Hydroperoxyoctadeca-9,11-dienoate; 13(S)-HPODE; 13S-Hydroperoxy-9Z,11E-octadecadienoic acid/9(S)-HPODE; 9(S)-HPOD; (10E,12Z)-(9S)-9-Hydroperoxyoctadeca-10,12-dienoic acid$$$13(S)-HODE; (13S)-Hydroxyoctadecadienoic acid; (9Z, 11E)-(13S)-13-Hydroxyoctadeca-9,11-dienoic acid/12(13)-EpOME; (12R,13S)-(9Z)-12,13-Epoxyoctadecenoic acid/9(10)-EpOME; (9R,10S)-(12Z)-9,10-Epoxyoctadecenoic acid$//13-OxoODE; 13-KODE; (9Z,11E)-13-Oxooctadeca-9,11-dienoic acid$/$//13-OxoODE; 13-KODE; (9Z,11E)-13-Oxooctadeca-9,11-dienoic acid</t>
+  </si>
+  <si>
+    <t>Sialic acid metabolism</t>
+  </si>
+  <si>
+    <t>E71,E1924,E1428,E689,E1426,E931</t>
+  </si>
+  <si>
+    <t>,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$</t>
+  </si>
+  <si>
+    <t>Leukotriene metabolism</t>
+  </si>
+  <si>
+    <t>E1227,E1250,E267,E196,E1004,E789,E195,E1237,E2005,E897,E1918,E193,E872,E790</t>
+  </si>
+  <si>
+    <t>,,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781,C00909,,,C00909,CE2567/CE2566/CE5178/CE4990/CE4876/CE5304/CE5349/CE6508/CE7080/CE7091/CE7097/CE7084/CE7083,,C00219,,C00909,,</t>
+  </si>
+  <si>
+    <t>$$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid$Leukotriene A4$$$Leukotriene A4$5(S),6(S)-epoxy-15(S)-hydroxy-7E,9E,11Z,13E-eicosatetraenoic acid anion/5(S),6(S)-epoxy-15(R)-hydroxyeicosatetraenoate/5-oxo-6-trans-leukotriene B4/12-oxo-leukotriene B4/delta12-Prostaglandin J2//5-oxo-6E-12-epi-LTB4/5-hydroperoxy-EPA/15(S)-hydroperoxy-EPE/15(R)-hydroperoxy-EPE/5-oxo-12(S)-hydroxy-eicosa-6E,8Z,10E,14Z-tetraenoate//leukotriene B5$$arachidonic acid$$Leukotriene A4$$</t>
+  </si>
+  <si>
+    <t>Beta-Alanine metabolism</t>
+  </si>
+  <si>
+    <t>E996,E1342,E1197</t>
+  </si>
+  <si>
+    <t>,,</t>
+  </si>
+  <si>
+    <t>$$</t>
+  </si>
+  <si>
+    <t>Omega-3 fatty acid metabolism</t>
+  </si>
+  <si>
+    <t>E484,E155</t>
+  </si>
+  <si>
+    <t>C06426/C06427,</t>
+  </si>
+  <si>
+    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$</t>
+  </si>
+  <si>
+    <t>Hexose phosphorylation</t>
+  </si>
+  <si>
+    <t>E1401,E1515,E689,E1551,E1554,E931</t>
+  </si>
+  <si>
+    <t>Limonene and pinene degradation</t>
+  </si>
+  <si>
+    <t>E616,E612,E903,E906</t>
+  </si>
+  <si>
+    <t>,,,</t>
+  </si>
+  <si>
+    <t>$$$</t>
+  </si>
+  <si>
+    <t>Prostaglandin formation from arachidonate</t>
+  </si>
+  <si>
+    <t>E1227,E120,E258,E160,E276,E1237,E927,E897,E267</t>
+  </si>
+  <si>
+    <t>,,,,,CE2567/CE2566/CE5178/CE4990/CE4876/CE5304/CE5349/CE6508/CE7080/CE7091/CE7097/CE7084/CE7083,,C00219,C05356/C00959/C04685/C04686/C05966/C05965/C14813/C02165/C04849/C14781</t>
+  </si>
+  <si>
+    <t>$$$$$5(S),6(S)-epoxy-15(S)-hydroxy-7E,9E,11Z,13E-eicosatetraenoic acid anion/5(S),6(S)-epoxy-15(R)-hydroxyeicosatetraenoate/5-oxo-6-trans-leukotriene B4/12-oxo-leukotriene B4/delta12-Prostaglandin J2//5-oxo-6E-12-epi-LTB4/5-hydroperoxy-EPA/15(S)-hydroperoxy-EPE/15(R)-hydroperoxy-EPE/5-oxo-12(S)-hydroxy-eicosa-6E,8Z,10E,14Z-tetraenoate//leukotriene B5$$arachidonic acid$5-Hydroperoxy-6-trans-8,11,14-cis-eicosatetraenoate/Prostaglandin B1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-10,13-dienoate; Prostaglandin A1; PGA1/(13E)-(15S)-15-Hydroxy-9-oxoprosta-11,13-dienoate; Prostaglandin C1/15(S)-HPETE; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoic acid; 15-Hydroperoxyeicosatetraenoate; 15-Hydroperoxyicosatetraenoate; 15-Hydroperoxyeicosatetraenoic acid; 15-Hydroperoxyicosatetraenoic acid; (5Z,8Z,11Z,13E)-(15S)-15-Hydroperoxyicosa-5,8,11,13-tetraenoate/12(S)-HPETE; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoic acid; (5Z,8Z,10E,14Z)-(12S)-12-Hydroperoxyicosa-5,8,10,14-tetraenoate; 12-Hydroperoxyeicosatetraenoate; 12-Hydroperoxyicosatetraenoate; 12-Hydroperoxyeicosatetraenoic acid; 12-Hydroperoxyicosatetraenoic acid/11H-14,15-EETA; 11-Hydroxy-14,15-EETA; 11-Hydroxy-14,15-epoxyeicosatrienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyeicosa-5,8,12-trienoic acid; (5Z,8Z,12E)-14,15-Epoxy-11-hydroxyicosa-5,8,12-trienoic acid/Leukotriene B4/(5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoic acid; (5Z,9E,14Z)-(8xi,11R,12S)-11,12-Epoxy-8-hydroxyicosa-5,9,14-trienoate; Hepoxilin A3/15H-11,12-EETA; 15-Hydroxy-11,12-epoxyeicosatrienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyeicosa-5,8,13-trienoic acid; (5Z,8Z,13E)-(15S)-11,12-Epoxy-15-hydroxyicosa-5,8,13-trienoic acid</t>
+  </si>
+  <si>
+    <t>Porphyrin metabolism</t>
+  </si>
+  <si>
+    <t>E466,E240,E463,E145</t>
   </si>
   <si>
     <t>Phosphatidylinositol phosphate metabolism</t>
   </si>
   <si>
-    <t>E2213,E689,E692,E1982,E275,E690,E75,E932</t>
-  </si>
-  <si>
-    <t>C15658,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C13747/C07480/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00055,C00249,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C01194,C00208/C00252/C00243/C01083/C00089/C01235/C05400/C05402</t>
-  </si>
-  <si>
-    <t>6-(alpha-D-Glucosaminyl)-1D-myo-inositol$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/1,7-Dimethylxanthine; Paraxanthine//alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$CMP$Hexadecanoate (n-C16:0)$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$Phosphatidylinositol$Maltose/Isomaltose; Brachiose/Lactose/Trehalose/Sucrose/1-alpha-D-Galactosyl-myo-inositol; 1-O-alpha-D-Galactosyl-D-myo-inositol; Galactinol/Epimelibiose/Melibiose</t>
-  </si>
-  <si>
-    <t>Sialic acid metabolism</t>
-  </si>
-  <si>
-    <t>E689,E692,E1982,E1932,E1436,E690,E75,E1434,E932,E1158</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C13747/C07480/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00055,C01674,C01074/C00645/C00140,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C01194,C01074/C00645/C00140,C00208/C00252/C00243/C01083/C00089/C01235/C05400/C05402,C05401</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/1,7-Dimethylxanthine; Paraxanthine//alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$CMP$Chitobiose$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$Phosphatidylinositol$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$Maltose/Isomaltose; Brachiose/Lactose/Trehalose/Sucrose/1-alpha-D-Galactosyl-myo-inositol; 1-O-alpha-D-Galactosyl-D-myo-inositol; Galactinol/Epimelibiose/Melibiose$3-beta-D-Galactosyl-sn-glycerol; Galactosylglycerol</t>
+    <t>E689,E71,E931</t>
+  </si>
+  <si>
+    <t>Keratan sulfate degradation</t>
+  </si>
+  <si>
+    <t>E1428,E1426</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>$</t>
+  </si>
+  <si>
+    <t>Lipoate metabolism</t>
+  </si>
+  <si>
+    <t>E228,E1011</t>
   </si>
   <si>
     <t>Drug metabolism - other enzymes</t>
   </si>
   <si>
-    <t>E1979,E633,E2093,E930</t>
-  </si>
-  <si>
-    <t>,,,</t>
-  </si>
-  <si>
-    <t>$$$</t>
+    <t>E2085,E632</t>
   </si>
   <si>
     <t>Starch and Sucrose Metabolism</t>
   </si>
   <si>
-    <t>E689,E692,E932,E690</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C13747/C07480/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00208/C00252/C00243/C01083/C00089/C01235/C05400/C05402,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/1,7-Dimethylxanthine; Paraxanthine//alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$Maltose/Isomaltose; Brachiose/Lactose/Trehalose/Sucrose/1-alpha-D-Galactosyl-myo-inositol; 1-O-alpha-D-Galactosyl-D-myo-inositol; Galactinol/Epimelibiose/Melibiose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose</t>
+    <t>E689,E931</t>
+  </si>
+  <si>
+    <t>Vitamin A (retinol) metabolism</t>
+  </si>
+  <si>
+    <t>E210,E203,E204,E189,E78</t>
+  </si>
+  <si>
+    <t>C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,,,,CE5932/C02075/C06428/CE5013</t>
+  </si>
+  <si>
+    <t>5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$$$$13,14-epoxy-retinol/Retinyl ester; all-trans-Retinyl ester/(5Z,8Z,11Z,14Z,17Z)-Icosapentaenoic acid; (5Z,8Z,11Z,14Z,17Z)-Eicosapentaenoic acid; Eicosapentaenoic acid; 5,8,11,14,17-Icosapentaenoic acid; (5Z,8Z,11Z,14Z,17Z)-Eicosapentaenoate/</t>
+  </si>
+  <si>
+    <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
+  </si>
+  <si>
+    <t>E1811,E1067,E111</t>
+  </si>
+  <si>
+    <t>Hyaluronan Metabolism</t>
+  </si>
+  <si>
+    <t>CoA Catabolism</t>
+  </si>
+  <si>
+    <t>E1067,E111</t>
+  </si>
+  <si>
+    <t>Heparan sulfate degradation</t>
+  </si>
+  <si>
+    <t>Biopterin metabolism</t>
+  </si>
+  <si>
+    <t>E701,E703,E405,E403,E776</t>
+  </si>
+  <si>
+    <t>,,,,</t>
+  </si>
+  <si>
+    <t>$$$$</t>
+  </si>
+  <si>
+    <t>Glycerophospholipid metabolism</t>
+  </si>
+  <si>
+    <t>E71,E484,E1576,E130,E897,E689,E210</t>
+  </si>
+  <si>
+    <t>,C06426/C06427,,,C00219,,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016</t>
+  </si>
+  <si>
+    <t>$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$$$arachidonic acid$$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol</t>
+  </si>
+  <si>
+    <t>N-Glycan Degradation</t>
+  </si>
+  <si>
+    <t>E689,E1428,E1426</t>
+  </si>
+  <si>
+    <t>Aminosugars metabolism</t>
+  </si>
+  <si>
+    <t>E1428,E1426,E1401</t>
+  </si>
+  <si>
+    <t>Glutathione Metabolism</t>
+  </si>
+  <si>
+    <t>E609</t>
+  </si>
+  <si>
+    <t>Prostaglandin formation from dihomo gama-linoleic acid</t>
+  </si>
+  <si>
+    <t>E1227</t>
+  </si>
+  <si>
+    <t>Omega-6 fatty acid metabolism</t>
+  </si>
+  <si>
+    <t>E897</t>
+  </si>
+  <si>
+    <t>C00219</t>
+  </si>
+  <si>
+    <t>arachidonic acid</t>
+  </si>
+  <si>
+    <t>Carnitine shuttle</t>
+  </si>
+  <si>
+    <t>E345,E1751,E1288,E335,E344,E2981</t>
+  </si>
+  <si>
+    <t>Galactose metabolism</t>
+  </si>
+  <si>
+    <t>E689,E1428,E1426,E931</t>
   </si>
   <si>
     <t>Glycosphingolipid metabolism</t>
   </si>
   <si>
-    <t>E689,E692,E1982,E137,E275,E690,E109,E1114,E1136</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C13747/C07480/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00055,,C00249,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,,,C05594</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/1,7-Dimethylxanthine; Paraxanthine//alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$CMP$$Hexadecanoate (n-C16:0)$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$$$3-Methoxy-4-hydroxyphenylethyleneglycol</t>
-  </si>
-  <si>
-    <t>Androgen and estrogen biosynthesis and metabolism</t>
-  </si>
-  <si>
-    <t>E2377,E1775,E187,E612,E94,E613,E95,E12,E302,E1285,E958,E1286,E959,E1543,E1301,E2463,E2589,E1546,E1709,E1829,E430,E1772,E184,E186</t>
-  </si>
-  <si>
-    <t>C05301/hestratriol/C05141/CE2179,,C03917/C05293/C00523/C04373/C04295,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,C11134/tststeroneglc,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,C18038/C05138/C04518/C05485,C18045/C14497/C18075/C05294/C05139,dhea/C03772/C01227/C00674/C00535,C04042/C01953/C03681,dhea/C03772/C01227/C00674/C00535,C04042/C01953/C03681,CE2186/CE2183/C05302/C05284/C05290/C05140,C05504,andrstndn/C00280,C00468,CE2186/CE2183/C05302/C05284/C05290/C05140,C00951,,CE2209,,C03917/C05293/C00523/C04373/C04295,C03917/C05293/C00523/C04373/C04295</t>
-  </si>
-  <si>
-    <t>2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)/testosterone glucuronide$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$/17alpha-Hydroxypregnenolone/17alpha,20alpha-Dihydroxypregn-4-en-3-one/21-Hydroxypregnenolone$/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$4-methoxy-17beta-estradiol/2-hydroxy-3-methoxy-17beta-estradiol/2-Methoxyestradiol-17beta/11beta-Hydroxyandrost-4-ene-3,17-dione; Androst-4-ene-3,17-dione-11beta-ol; 4-Androsten-11beta-ol-3,17-dione/19-Hydroxyandrost-4-ene-3,17-dione; 19-Hydroxyandrostenedione/16alpha-Hydroxyandrost-4-ene-3,17-dione; 4-Androsten-16alpha-ol-3,17-dione$16-Glucuronide-estriol; 16alpha,17beta-Estriol 16-(beta-D-glucuronide)$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$Estrone; 3-Hydroxy-1,3,5(10)-estratrien-17-one$4-methoxy-17beta-estradiol/2-hydroxy-3-methoxy-17beta-estradiol/2-Methoxyestradiol-17beta/11beta-Hydroxyandrost-4-ene-3,17-dione; Androst-4-ene-3,17-dione-11beta-ol; 4-Androsten-11beta-ol-3,17-dione/19-Hydroxyandrost-4-ene-3,17-dione; 19-Hydroxyandrostenedione/16alpha-Hydroxyandrost-4-ene-3,17-dione; 4-Androsten-16alpha-ol-3,17-dione$Estradiol-17beta; beta-Estradiol; Estradiol$$5alpha-androstane-3alpha,17beta-diol$$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol</t>
-  </si>
-  <si>
-    <t>Limonene and pinene degradation</t>
-  </si>
-  <si>
-    <t>E900,E621,E904,E907,E905,E617,E620</t>
+    <t>E1106,E689,E132,E130</t>
+  </si>
+  <si>
+    <t>Alkaloid biosynthesis II</t>
+  </si>
+  <si>
+    <t>E414,E412</t>
+  </si>
+  <si>
+    <t>Drug metabolism - cytochrome P450</t>
+  </si>
+  <si>
+    <t>E937,E1833,E782,E450,E1606,E286,E429,E1723,E1726</t>
+  </si>
+  <si>
+    <t>,,,,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$$$</t>
+  </si>
+  <si>
+    <t>Bile acid biosynthesis</t>
+  </si>
+  <si>
+    <t>E951,E381,E834,E487,E383</t>
+  </si>
+  <si>
+    <t>Putative anti-Inflammatory metabolites formation from EPA</t>
+  </si>
+  <si>
+    <t>E1237,E1898</t>
+  </si>
+  <si>
+    <t>CE2567/CE2566/CE5178/CE4990/CE4876/CE5304/CE5349/CE6508/CE7080/CE7091/CE7097/CE7084/CE7083,</t>
+  </si>
+  <si>
+    <t>5(S),6(S)-epoxy-15(S)-hydroxy-7E,9E,11Z,13E-eicosatetraenoic acid anion/5(S),6(S)-epoxy-15(R)-hydroxyeicosatetraenoate/5-oxo-6-trans-leukotriene B4/12-oxo-leukotriene B4/delta12-Prostaglandin J2//5-oxo-6E-12-epi-LTB4/5-hydroperoxy-EPA/15(S)-hydroperoxy-EPE/15(R)-hydroperoxy-EPE/5-oxo-12(S)-hydroxy-eicosa-6E,8Z,10E,14Z-tetraenoate//leukotriene B5$</t>
+  </si>
+  <si>
+    <t>Pentose and Glucuronate Interconversions</t>
+  </si>
+  <si>
+    <t>E2166</t>
+  </si>
+  <si>
+    <t>Aspartate and asparagine metabolism</t>
+  </si>
+  <si>
+    <t>E227,E609,E847,E1197</t>
+  </si>
+  <si>
+    <t>Histidine metabolism</t>
+  </si>
+  <si>
+    <t>E996,E1342,E358</t>
+  </si>
+  <si>
+    <t>Vitamin B6 (pyridoxine) metabolism</t>
+  </si>
+  <si>
+    <t>E1026,E1859,E1081</t>
+  </si>
+  <si>
+    <t>Caffeine metabolism</t>
+  </si>
+  <si>
+    <t>E693,E1853</t>
+  </si>
+  <si>
+    <t>D4&amp;E4-neuroprostanes formation</t>
+  </si>
+  <si>
+    <t>E1532,E273</t>
+  </si>
+  <si>
+    <t>Propanoate metabolism</t>
+  </si>
+  <si>
+    <t>E1011</t>
+  </si>
+  <si>
+    <t>Ascorbate (Vitamin C) and Aldarate Metabolism</t>
+  </si>
+  <si>
+    <t>E2334,E2166,E711,E1011</t>
+  </si>
+  <si>
+    <t>Vitamin B9 (folate) metabolism</t>
+  </si>
+  <si>
+    <t>E655,E982</t>
+  </si>
+  <si>
+    <t>Fructose and mannose metabolism</t>
+  </si>
+  <si>
+    <t>E689,E496,E1620</t>
+  </si>
+  <si>
+    <t>Pentose phosphate pathway</t>
+  </si>
+  <si>
+    <t>E689,E2166</t>
+  </si>
+  <si>
+    <t>Vitamin D3 (cholecalciferol) metabolism</t>
+  </si>
+  <si>
+    <t>E1300</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - ganglioseries</t>
+  </si>
+  <si>
+    <t>E1543</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - globoseries</t>
+  </si>
+  <si>
+    <t>E689</t>
+  </si>
+  <si>
+    <t>Vitamin E metabolism</t>
+  </si>
+  <si>
+    <t>E1886</t>
+  </si>
+  <si>
+    <t>Fatty acid activation</t>
+  </si>
+  <si>
+    <t>E484</t>
+  </si>
+  <si>
+    <t>C06426/C06427</t>
+  </si>
+  <si>
+    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate</t>
+  </si>
+  <si>
+    <t>Vitamin B2 (riboflavin) metabolism</t>
+  </si>
+  <si>
+    <t>E365</t>
+  </si>
+  <si>
+    <t>Vitamin B3 (nicotinate and nicotinamide) metabolism</t>
+  </si>
+  <si>
+    <t>E1696</t>
+  </si>
+  <si>
+    <t>Urea cycle/amino group metabolism</t>
+  </si>
+  <si>
+    <t>E768,E1197,E569,E769,E570,E576,E1188</t>
   </si>
   <si>
     <t>,,,,,,</t>
@@ -133,736 +487,229 @@
     <t>$$$$$$</t>
   </si>
   <si>
-    <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
-  </si>
-  <si>
-    <t>E1819,E119,E1069,E1075,E1818,E118</t>
-  </si>
-  <si>
-    <t>,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$</t>
-  </si>
-  <si>
-    <t>Glycerophospholipid metabolism</t>
-  </si>
-  <si>
-    <t>E689,E1583,E1982,E692,E489,E898,E137,E690,E1584,E75,E2448,E1158,E1136,E215</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C13747/C07480/C00984/C00159,,C00055,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,,,,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,,C01194,,C05401,C05594,</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/1,7-Dimethylxanthine; Paraxanthine//alpha-D-Galactose/D-Mannose$$CMP$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$$$$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$$Phosphatidylinositol$$3-beta-D-Galactosyl-sn-glycerol; Galactosylglycerol$3-Methoxy-4-hydroxyphenylethyleneglycol$</t>
-  </si>
-  <si>
-    <t>De novo fatty acid biosynthesis</t>
-  </si>
-  <si>
-    <t>E489,E82,E898,E275,E913</t>
-  </si>
-  <si>
-    <t>,,,C00249,</t>
-  </si>
-  <si>
-    <t>$$$Hexadecanoate (n-C16:0)$</t>
-  </si>
-  <si>
-    <t>Hexose phosphorylation</t>
-  </si>
-  <si>
-    <t>E689,E692,E1556,E1561,E690,E1559,E1562,E932,E1409,E1523</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C13747/C07480/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C02763/C00166,C02763/C00166,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C02763/C00166,C02763/C00166,C00208/C00252/C00243/C01083/C00089/C01235/C05400/C05402,,</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/1,7-Dimethylxanthine; Paraxanthine//alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$enol-Phenylpyruvate/Phenylpyruvate$enol-Phenylpyruvate/Phenylpyruvate$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$enol-Phenylpyruvate/Phenylpyruvate$enol-Phenylpyruvate/Phenylpyruvate$Maltose/Isomaltose; Brachiose/Lactose/Trehalose/Sucrose/1-alpha-D-Galactosyl-myo-inositol; 1-O-alpha-D-Galactosyl-D-myo-inositol; Galactinol/Epimelibiose/Melibiose$$</t>
-  </si>
-  <si>
-    <t>Biopterin metabolism</t>
-  </si>
-  <si>
-    <t>E703,E2139,E773,E776,E2511,E410,E777,E702,E704,E408</t>
-  </si>
-  <si>
-    <t>C00082/CE2174,,C00079/CE2172,C00079/CE2172,C00268,CE2705/CE5236,C00079/CE2172,C00082/CE2174,C00082/CE2174,CE2705/CE5236</t>
-  </si>
-  <si>
-    <t>L-Tyrosine/$$L-Phenylalanine/$L-Phenylalanine/$6,7-Dihydrobiopterin$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$L-Phenylalanine/$L-Tyrosine/$L-Tyrosine/$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - globoseries</t>
-  </si>
-  <si>
-    <t>E689,E692,E1982,E690</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C13747/C07480/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00055,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/1,7-Dimethylxanthine; Paraxanthine//alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$CMP$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose</t>
-  </si>
-  <si>
-    <t>CoA Catabolism</t>
-  </si>
-  <si>
-    <t>E1069,E118,E1075,E119</t>
-  </si>
-  <si>
-    <t>Beta-Alanine metabolism</t>
-  </si>
-  <si>
-    <t>E1350,E1000,E1003,E1205</t>
+    <t>Glycolysis and Gluconeogenesis</t>
+  </si>
+  <si>
+    <t>3-oxo-10R-octadecatrienoate beta-oxidation</t>
+  </si>
+  <si>
+    <t>E46</t>
+  </si>
+  <si>
+    <t>Butanoate metabolism</t>
+  </si>
+  <si>
+    <t>E1438</t>
+  </si>
+  <si>
+    <t>Arginine and Proline Metabolism</t>
+  </si>
+  <si>
+    <t>E1188</t>
+  </si>
+  <si>
+    <t>Ubiquinone Biosynthesis</t>
+  </si>
+  <si>
+    <t>E1551,E1554</t>
+  </si>
+  <si>
+    <t>N-Glycan biosynthesis</t>
   </si>
   <si>
     <t>Tryptophan metabolism</t>
   </si>
   <si>
-    <t>E1603,E517,E1412,E670,E399,E2418,E2511,E671,E730,E942,E1144,E519,E591,E2390,E1857,E401,E1858,E297,E1664,E1945,E1146,E593,E557,E2250,E376,E853,E1768,E594,E1769,E2242,E947,E1843,E596,E1960,E552,E1266,E1025,E667,E2104,E1476,E1357,E2254,E561,E1761,E1601,E2584,E1951,E1269,E1602,E728,E2246,E1661</t>
-  </si>
-  <si>
-    <t>CE2119/C05643,CE5860,C05635/C16596,C05642,C00078/C00525,C01717,C00268,C05642,C06212,C00328/C05647,,CE5860,CE3140,CE2153,CE5538/C05653,C00078/C00525,CE5538/C05653,C00954/C05634,C02693,C00331,,CE3140,C05660,C05639,C01598,CE1918,CE6205,CE3140,CE6205,C00978,C00328/C05647,C02406/C02700,CE3140,C00637,CE2122,,C01252,C05642,C05638,CE3087,CE5982,C05639,C05660,CE6205,CE2119/C05643,C00643,C00780,,CE2119/C05643,C06212,C00978,C02693</t>
-  </si>
-  <si>
-    <t>/6-Hydroxymelatonin$$5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione$Formyl-N-acetyl-5-methoxykynurenamine$L-Tryptophan/D-Tryptophan$4-Hydroxy-2-quinolinecarboxylic acid$6,7-Dihydrobiopterin$Formyl-N-acetyl-5-methoxykynurenamine$N-Methylserotonin$L-Kynurenine/Formyl-5-hydroxykynurenamine$$$$$noradrenochrome/N-Formylanthranilate$L-Tryptophan/D-Tryptophan$noradrenochrome/N-Formylanthranilate$Indole-3-acetate/5-Hydroxyindoleacetaldehyde$Indole-3-acetamide$Indolepyruvate; Indolepyruvic acid; (Indol-3-yl)pyruvate; Indole-3-pyruvate; 3-(Indol-3-yl)pyruvate$$$5-Methoxyindoleacetate$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$Melatonin; N-Acetyl-5-methoxytryptamine$5-hydroxytryptophol$5-methoxytryptophol$$5-methoxytryptophol$N-Acetylserotonin; N-Acetyl-5-hydroxytryptamine$L-Kynurenine/Formyl-5-hydroxykynurenamine$Formylkynurenine/L-Formylkynurenine$$Indole-3-acetaldehyde$methyl indole-3-acetate$$4-(2-Aminophenyl)-2,4-dioxobutanoate$Formyl-N-acetyl-5-methoxykynurenamine$5-Hydroxykynurenamine$beta-carboline$$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$5-Methoxyindoleacetate$5-methoxytryptophol$/6-Hydroxymelatonin$5-Hydroxy-L-tryptophan$Serotonin$$/6-Hydroxymelatonin$N-Methylserotonin$N-Acetylserotonin; N-Acetyl-5-hydroxytryptamine$Indole-3-acetamide</t>
-  </si>
-  <si>
-    <t>Alkaloid biosynthesis II</t>
-  </si>
-  <si>
-    <t>E415,E413,E419,E417</t>
+    <t>E556,E1258,E852,E1349,E1468,E1018,E2096,E946,E547,E512,E394,E1653,E1594,E514,E586,E292,E1849,E588,E727,E371,E1937,E729</t>
+  </si>
+  <si>
+    <t>,,,,,,,,,,,,,,,,,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$$$$$$$$$$$$$$$$</t>
+  </si>
+  <si>
+    <t>Xenobiotics metabolism</t>
+  </si>
+  <si>
+    <t>E1965</t>
+  </si>
+  <si>
+    <t>Glycine, serine, alanine and threonine metabolism</t>
+  </si>
+  <si>
+    <t>E2336,E707</t>
+  </si>
+  <si>
+    <t>Tyrosine metabolism</t>
+  </si>
+  <si>
+    <t>E1865,E1077,E918,E1853,E429,E1086,E852,E701,E21,E768,E769,E58,E1163,E1559,E703,E693,E1185,E25,E36,E1561,E1433,E1551,E539,E1849,E530,E541,E1554,E776</t>
+  </si>
+  <si>
+    <t>,,,,,,,,,,,,,,,,,,,,,,,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$$$$$$$$$$$$$$$$$$$$$$</t>
+  </si>
+  <si>
+    <t>Methionine and cysteine metabolism</t>
+  </si>
+  <si>
+    <t>Purine metabolism</t>
+  </si>
+  <si>
+    <t>E501,E1800,E1481</t>
+  </si>
+  <si>
+    <t>R Group Synthesis</t>
+  </si>
+  <si>
+    <t>C5-Branched dibasic acid metabolism</t>
+  </si>
+  <si>
+    <t>Pyruvate Metabolism</t>
+  </si>
+  <si>
+    <t>Chondroitin sulfate degradation</t>
+  </si>
+  <si>
+    <t>Di-unsaturated fatty acid beta-oxidation</t>
+  </si>
+  <si>
+    <t>Squalene and cholesterol biosynthesis</t>
+  </si>
+  <si>
+    <t>Glycerolipid metabolism</t>
+  </si>
+  <si>
+    <t>Vitamin B1 (thiamin) metabolism</t>
+  </si>
+  <si>
+    <t>Glycosylphosphatidylinositol(GPI)-anchor biosynthesis</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - lactoseries</t>
+  </si>
+  <si>
+    <t>Parathio degradation</t>
+  </si>
+  <si>
+    <t>Blood Group Biosynthesis</t>
+  </si>
+  <si>
+    <t>Electron transport chain</t>
+  </si>
+  <si>
+    <t>Vitamin H (biotin) metabolism</t>
+  </si>
+  <si>
+    <t>Heparan sulfate biosynthesis</t>
+  </si>
+  <si>
+    <t>Glyoxylate and Dicarboxylate Metabolism</t>
+  </si>
+  <si>
+    <t>Valine, leucine and isoleucine degradation</t>
+  </si>
+  <si>
+    <t>Fatty Acid Metabolism</t>
+  </si>
+  <si>
+    <t>Glycosaminoglycan degradation</t>
+  </si>
+  <si>
+    <t>Fatty acid oxidation</t>
+  </si>
+  <si>
+    <t>ROS Detoxification</t>
   </si>
   <si>
     <t>Saturated fatty acids beta-oxidation</t>
   </si>
   <si>
-    <t>E275</t>
-  </si>
-  <si>
-    <t>C00249</t>
-  </si>
-  <si>
-    <t>Hexadecanoate (n-C16:0)</t>
+    <t>Mono-unsaturated fatty acid beta-oxidation</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - neolactoseries</t>
+  </si>
+  <si>
+    <t>Geraniol degradation</t>
+  </si>
+  <si>
+    <t>Vitamin D</t>
+  </si>
+  <si>
+    <t>Dynorphin metabolism</t>
+  </si>
+  <si>
+    <t>Fatty acid oxidation, peroxisome</t>
+  </si>
+  <si>
+    <t>Polyunsaturated fatty acid biosynthesis</t>
+  </si>
+  <si>
+    <t>Alanine and Aspartate Metabolism</t>
   </si>
   <si>
     <t>Keratan sulfate biosynthesis</t>
   </si>
   <si>
-    <t>E1982</t>
-  </si>
-  <si>
-    <t>C00055</t>
-  </si>
-  <si>
-    <t>CMP</t>
+    <t>TCA cycle</t>
+  </si>
+  <si>
+    <t>3-Chloroacrylic acid degradation</t>
+  </si>
+  <si>
+    <t>Sphingolipid metabolism</t>
   </si>
   <si>
     <t>O-Glycan biosynthesis</t>
   </si>
   <si>
-    <t>Tyrosine metabolism</t>
-  </si>
-  <si>
-    <t>E2257,E670,E144,E776,E1569,E2511,E1441,E671,E1559,E777,E531,E1747,E2305,E543,E1857,E767,E2275,E1622,E2260,E21,E544,E1443,E919,E1561,E1858,E2154,E2400,E533,E697,E545,E2307,E1779,E1562,E853,E702,E1873,E546,E1136,E769,E535,E703,E1085,E770,E1861,E1149,E25,E2535,E1875,E36,E1565,E1094,E704,E667,E1095,E694,E434,E62,E1556,E773,E1171,E1567,E1096,E1193,E2256,E2407,E2131,E1097</t>
-  </si>
-  <si>
-    <t>CE5536,C05642,CE5025,C00079/CE2172,C05583/C05582,C00268,C03758,C05642,C02763/C00166,C00079/CE2172,C05588,,C00547,C09642,CE5538/C05653,C05589/C00788,C05350/C01179,,CE5536,CE2176,C09642,C03758,,C02763/C00166,CE5538/C05653,C05587/C07453,C04043/C00642/C05852,C05588,CE5541,C09642,C00547,C05584,C02763/C00166,CE1918,C00082/CE2174,C00355,C09642,C05594,C05589/C00788,C05588,C00082/CE2174,CE4888,C05589/C00788,CE5542,C03711,CE2176,,C00355,C13690,C05583/C05582,C00822/C05604,C00082/CE2174,C05642,C00822/C05604,CE5541,C16586/CE2173,C05580,C02763/C00166,C00079/CE2172,C05577/C00544/C01161,C05583/C05582,C00822/C05604,CE5277,CE5536,C05576,CE5276,C00822/C05604</t>
-  </si>
-  <si>
-    <t>adrenochrome$Formyl-N-acetyl-5-methoxykynurenamine$5-S-glutathionyl-dopamine$L-Phenylalanine/$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$6,7-Dihydrobiopterin$Dopamine$Formyl-N-acetyl-5-methoxykynurenamine$enol-Phenylpyruvate/Phenylpyruvate$L-Phenylalanine/$L-Metanephrine$$Norepinephrine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$noradrenochrome/N-Formylanthranilate$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$2-Hydroxy-3-(4-hydroxyphenyl)propenoate; 4-Hydroxy-enol-phenylpyruvate/3-(4-Hydroxyphenyl)pyruvate$$adrenochrome$3-O-methyldopa$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$Dopamine$$enol-Phenylpyruvate/Phenylpyruvate$noradrenochrome/N-Formylanthranilate$3-Methoxytyramine/Epinine; Deoxyepinephrine$3,4-Dihydroxyphenylacetaldehyde; Protocatechuatealdehyde/4-Hydroxyphenylacetate/2-Hydroxyphenylacetate$L-Metanephrine$adrenochrome o-semiquinone$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$Norepinephrine$3-Methoxy-4-hydroxymandelate; Vanillylmandelic acid$enol-Phenylpyruvate/Phenylpyruvate$5-hydroxytryptophol$L-Tyrosine/$3,4-Dihydroxy-L-phenylalanine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$3-Methoxy-4-hydroxyphenylethyleneglycol$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Metanephrine$L-Tyrosine/$dopaminochrome$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$noradrenochrome o-semiquinone$N-Methylphenylethanolamine$3-O-methyldopa$$3,4-Dihydroxy-L-phenylalanine$Dopamine 3-O-sulfate$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$L-Tyrosine/$Formyl-N-acetyl-5-methoxykynurenamine$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$adrenochrome o-semiquinone$2-Phenyl-1,3-propanediol monocarbamate/$3,4-Dihydroxymandelate$enol-Phenylpyruvate/Phenylpyruvate$L-Phenylalanine/$3,4-Dihydroxymandelaldehyde/Homogentisate/3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$aminochrome o-semiquinone$adrenochrome$3,4-Dihydroxyphenylethyleneglycol$dopamine o-quinone$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome</t>
-  </si>
-  <si>
-    <t>Galactose metabolism</t>
-  </si>
-  <si>
-    <t>E689,E692,E1436,E690,E1434,E932,E1158</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C13747/C07480/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C01074/C00645/C00140,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C01074/C00645/C00140,C00208/C00252/C00243/C01083/C00089/C01235/C05400/C05402,C05401</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/1,7-Dimethylxanthine; Paraxanthine//alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$Maltose/Isomaltose; Brachiose/Lactose/Trehalose/Sucrose/1-alpha-D-Galactosyl-myo-inositol; 1-O-alpha-D-Galactosyl-D-myo-inositol; Galactinol/Epimelibiose/Melibiose$3-beta-D-Galactosyl-sn-glycerol; Galactosylglycerol</t>
-  </si>
-  <si>
-    <t>N-Glycan biosynthesis</t>
-  </si>
-  <si>
-    <t>E689,E692,E2007,E1982,E690</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C13747/C07480/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,,C00055,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/1,7-Dimethylxanthine; Paraxanthine//alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$$CMP$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose</t>
-  </si>
-  <si>
-    <t>N-Glycan Degradation</t>
-  </si>
-  <si>
-    <t>E689,E692,E1436,E690,E1434</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C13747/C07480/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C01074/C00645/C00140,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C01074/C00645/C00140</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/1,7-Dimethylxanthine; Paraxanthine//alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine</t>
-  </si>
-  <si>
-    <t>Histidine metabolism</t>
-  </si>
-  <si>
-    <t>E363,E2482,E1000,E1003,E361,E1350</t>
-  </si>
-  <si>
-    <t>Vitamin B6 (pyridoxine) metabolism</t>
-  </si>
-  <si>
-    <t>E1868,E2307,E1089,E1033,E1867,E2305</t>
-  </si>
-  <si>
-    <t>,C00547,,,,C00547</t>
-  </si>
-  <si>
-    <t>$Norepinephrine$$$$Norepinephrine</t>
-  </si>
-  <si>
-    <t>Hyaluronan Metabolism</t>
-  </si>
-  <si>
-    <t>E738,E1434,E1436</t>
-  </si>
-  <si>
-    <t>,C01074/C00645/C00140,C01074/C00645/C00140</t>
-  </si>
-  <si>
-    <t>$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - ganglioseries</t>
-  </si>
-  <si>
-    <t>E1551,E1982,E1550</t>
-  </si>
-  <si>
-    <t>,C00055,</t>
-  </si>
-  <si>
-    <t>$CMP$</t>
-  </si>
-  <si>
-    <t>Arachidonic acid metabolism</t>
-  </si>
-  <si>
-    <t>E199,E272,E977,E489,E1232,E898,E197,E200,E1245,E215</t>
-  </si>
-  <si>
-    <t>,,,,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$$$</t>
-  </si>
-  <si>
-    <t>Caffeine metabolism</t>
-  </si>
-  <si>
-    <t>E689,E697,E694,E1861</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C13747/C07480/C00984/C00159,CE5541,CE5541,CE5542</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/1,7-Dimethylxanthine; Paraxanthine//alpha-D-Galactose/D-Mannose$adrenochrome o-semiquinone$adrenochrome o-semiquinone$noradrenochrome o-semiquinone</t>
-  </si>
-  <si>
-    <t>Pentose phosphate pathway</t>
-  </si>
-  <si>
-    <t>E689,E692,E690,E2063,E2174</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C13747/C07480/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,,</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/1,7-Dimethylxanthine; Paraxanthine//alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$$</t>
-  </si>
-  <si>
-    <t>Linoleate metabolism</t>
-  </si>
-  <si>
-    <t>E1899,E763,E304,E307,E321,E1386,E489,E2205,E1918,E761,E2554,E308,E322,E1677,E647,E2129,E1388</t>
-  </si>
-  <si>
-    <t>,,,,,,,,,,,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$$$$$$$$$$</t>
-  </si>
-  <si>
-    <t>Urea cycle/amino group metabolism</t>
-  </si>
-  <si>
-    <t>E2257,E567,E2260,E1196,E2374,E2556,E770,E1149,E574,E769,E2307,E2256,E575,E2305,E581,E767,E1205</t>
-  </si>
-  <si>
-    <t>CE5536,,CE5536,,,,C05589/C00788,C03711,,C05589/C00788,C00547,CE5536,,C00547,,C05589/C00788,</t>
-  </si>
-  <si>
-    <t>adrenochrome$$adrenochrome$$$$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$N-Methylphenylethanolamine$$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$Norepinephrine$adrenochrome$$Norepinephrine$$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$</t>
-  </si>
-  <si>
-    <t>Omega-3 fatty acid metabolism</t>
-  </si>
-  <si>
-    <t>E489,E160</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>$</t>
-  </si>
-  <si>
-    <t>Vitamin B2 (riboflavin) metabolism</t>
-  </si>
-  <si>
-    <t>E370,E1169,E1165</t>
-  </si>
-  <si>
-    <t>,,</t>
-  </si>
-  <si>
-    <t>$$</t>
-  </si>
-  <si>
-    <t>Glycolysis and Gluconeogenesis</t>
-  </si>
-  <si>
-    <t>E2501,E689,E692,E690</t>
-  </si>
-  <si>
-    <t>,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C13747/C07480/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159</t>
-  </si>
-  <si>
-    <t>$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/1,7-Dimethylxanthine; Paraxanthine//alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose</t>
-  </si>
-  <si>
-    <t>Bile acid biosynthesis</t>
-  </si>
-  <si>
-    <t>E492,E388,E953,E835,E386,E831,E491,E952</t>
-  </si>
-  <si>
-    <t>,,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$</t>
-  </si>
-  <si>
-    <t>Leukotriene metabolism</t>
-  </si>
-  <si>
-    <t>E199,E1245,E272,E977,E2013,E790,E898,E875,E197,E200,E1926,E791,E873,E1235,E1258,E1011,E874</t>
-  </si>
-  <si>
-    <t>Squalene and cholesterol biosynthesis</t>
-  </si>
-  <si>
-    <t>E2353,E1491,E2007</t>
-  </si>
-  <si>
-    <t>Aminosugars metabolism</t>
-  </si>
-  <si>
-    <t>E1409,E1436,E1434,E1982</t>
-  </si>
-  <si>
-    <t>,C01074/C00645/C00140,C01074/C00645/C00140,C00055</t>
-  </si>
-  <si>
-    <t>$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$CMP</t>
-  </si>
-  <si>
-    <t>Keratan sulfate degradation</t>
-  </si>
-  <si>
-    <t>E1436,E1434</t>
-  </si>
-  <si>
-    <t>C01074/C00645/C00140,C01074/C00645/C00140</t>
-  </si>
-  <si>
-    <t>N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine</t>
-  </si>
-  <si>
-    <t>Lipoate metabolism</t>
-  </si>
-  <si>
-    <t>E1018,E233</t>
-  </si>
-  <si>
-    <t>Drug metabolism - cytochrome P450</t>
-  </si>
-  <si>
-    <t>E783,E1412,E1614,E782,E2566,E1224,E455,E1841,E1731,E780,E1734,E291,E938,E434</t>
-  </si>
-  <si>
-    <t>C16591,C05635/C16596,C16609,C16591,,C07572,,C16608,,C16591,,C16595/C16587,,C16586/CE2173</t>
-  </si>
-  <si>
-    <t>3-Carbamoyl-2-phenylpropionic acid$5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione$Didemethylcitalopram$3-Carbamoyl-2-phenylpropionic acid$$Citalopram$$Demethylcitalopram$$3-Carbamoyl-2-phenylpropionic acid$$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one/3-Carbamoyl-2-phenylpropionaldehyde$$2-Phenyl-1,3-propanediol monocarbamate/</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - lactoseries</t>
-  </si>
-  <si>
-    <t>Blood Group Biosynthesis</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - neolactoseries</t>
-  </si>
-  <si>
-    <t>Glutathione Metabolism</t>
-  </si>
-  <si>
-    <t>E614</t>
-  </si>
-  <si>
-    <t>Prostaglandin formation from dihomo gama-linoleic acid</t>
-  </si>
-  <si>
-    <t>E1235</t>
-  </si>
-  <si>
-    <t>Omega-6 fatty acid metabolism</t>
-  </si>
-  <si>
-    <t>E898</t>
-  </si>
-  <si>
-    <t>Aspartate and asparagine metabolism</t>
-  </si>
-  <si>
-    <t>E2374,E1205,E232,E614,E2556,E848</t>
-  </si>
-  <si>
-    <t>Xenobiotics metabolism</t>
-  </si>
-  <si>
-    <t>E182,E1745,E1973,E275</t>
-  </si>
-  <si>
-    <t>,,,C00249</t>
-  </si>
-  <si>
-    <t>$$$Hexadecanoate (n-C16:0)</t>
+    <t>Proteoglycan biosynthesis</t>
+  </si>
+  <si>
+    <t>Vitamin K metabolism</t>
+  </si>
+  <si>
+    <t>Glutamate metabolism</t>
+  </si>
+  <si>
+    <t>Benzoate degradation via CoA ligation</t>
+  </si>
+  <si>
+    <t>Dimethyl-branched-chain fatty acid mitochondrial beta-oxidation</t>
+  </si>
+  <si>
+    <t>Atrazine degradation</t>
+  </si>
+  <si>
+    <t>Vitamin B12 (cyanocobalamin) metabolism</t>
+  </si>
+  <si>
+    <t>Carbon fixation</t>
+  </si>
+  <si>
+    <t>Nucleotide Sugar Metabolism</t>
+  </si>
+  <si>
+    <t>1- and 2-Methylnaphthalene degradation</t>
+  </si>
+  <si>
+    <t>Pyrimidine metabolism</t>
+  </si>
+  <si>
+    <t>Nitrogen metabolism</t>
+  </si>
+  <si>
+    <t>Trihydroxycoprostanoyl-CoA beta-oxidation</t>
+  </si>
+  <si>
+    <t>Phytanic acid peroxisomal oxidation</t>
   </si>
   <si>
     <t>Lysine metabolism</t>
-  </si>
-  <si>
-    <t>E719,E1339,E2556,E441</t>
-  </si>
-  <si>
-    <t>D4&amp;E4-neuroprostanes formation</t>
-  </si>
-  <si>
-    <t>E1936,E278,E1540</t>
-  </si>
-  <si>
-    <t>Vitamin B1 (thiamin) metabolism</t>
-  </si>
-  <si>
-    <t>E2501,E1339</t>
-  </si>
-  <si>
-    <t>Vitamin E metabolism</t>
-  </si>
-  <si>
-    <t>E1894,E1892</t>
-  </si>
-  <si>
-    <t>Heparan sulfate degradation</t>
-  </si>
-  <si>
-    <t>Fatty acid activation</t>
-  </si>
-  <si>
-    <t>E489,E275</t>
-  </si>
-  <si>
-    <t>,C00249</t>
-  </si>
-  <si>
-    <t>$Hexadecanoate (n-C16:0)</t>
-  </si>
-  <si>
-    <t>Carnitine shuttle</t>
-  </si>
-  <si>
-    <t>E340,E1759,E346,E349,E1296,E718,E350,E348</t>
-  </si>
-  <si>
-    <t>Prostaglandin formation from arachidonate</t>
-  </si>
-  <si>
-    <t>E272,E977,E928,E898,E263,E165,E281,E1235,E163,E1245,E127</t>
-  </si>
-  <si>
-    <t>,,,,,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$$$$</t>
-  </si>
-  <si>
-    <t>Porphyrin metabolism</t>
-  </si>
-  <si>
-    <t>E245,E468,E471,E150</t>
-  </si>
-  <si>
-    <t>Valine, leucine and isoleucine degradation</t>
-  </si>
-  <si>
-    <t>E1986</t>
-  </si>
-  <si>
-    <t>Fatty Acid Metabolism</t>
-  </si>
-  <si>
-    <t>Pentose and Glucuronate Interconversions</t>
-  </si>
-  <si>
-    <t>E2174</t>
-  </si>
-  <si>
-    <t>Butanoate metabolism</t>
-  </si>
-  <si>
-    <t>E2297,E1445,E1446</t>
-  </si>
-  <si>
-    <t>Fructose and mannose metabolism</t>
-  </si>
-  <si>
-    <t>E1628,E689,E692,E690,E501</t>
-  </si>
-  <si>
-    <t>,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C13747/C07480/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159,</t>
-  </si>
-  <si>
-    <t>$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/1,7-Dimethylxanthine; Paraxanthine//alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose$</t>
-  </si>
-  <si>
-    <t>Vitamin A (retinol) metabolism</t>
-  </si>
-  <si>
-    <t>E207,E193,E82,E208,E215</t>
-  </si>
-  <si>
-    <t>,,,,</t>
-  </si>
-  <si>
-    <t>$$$$</t>
-  </si>
-  <si>
-    <t>Ubiquinone Biosynthesis</t>
-  </si>
-  <si>
-    <t>E1556,E1561,E1559,E1562,E2275</t>
-  </si>
-  <si>
-    <t>C02763/C00166,C02763/C00166,C02763/C00166,C02763/C00166,C05350/C01179</t>
-  </si>
-  <si>
-    <t>enol-Phenylpyruvate/Phenylpyruvate$enol-Phenylpyruvate/Phenylpyruvate$enol-Phenylpyruvate/Phenylpyruvate$enol-Phenylpyruvate/Phenylpyruvate$2-Hydroxy-3-(4-hydroxyphenyl)propenoate; 4-Hydroxy-enol-phenylpyruvate/3-(4-Hydroxyphenyl)pyruvate</t>
-  </si>
-  <si>
-    <t>Propanoate metabolism</t>
-  </si>
-  <si>
-    <t>E1018</t>
-  </si>
-  <si>
-    <t>Putative anti-Inflammatory metabolites formation from EPA</t>
-  </si>
-  <si>
-    <t>E1906,E1245</t>
-  </si>
-  <si>
-    <t>3-oxo-10R-octadecatrienoate beta-oxidation</t>
-  </si>
-  <si>
-    <t>E46,E51</t>
-  </si>
-  <si>
-    <t>Vitamin B9 (folate) metabolism</t>
-  </si>
-  <si>
-    <t>E989,E656</t>
-  </si>
-  <si>
-    <t>Arginine and Proline Metabolism</t>
-  </si>
-  <si>
-    <t>E1196,E2556</t>
-  </si>
-  <si>
-    <t>Vitamin D3 (cholecalciferol) metabolism</t>
-  </si>
-  <si>
-    <t>E1308</t>
-  </si>
-  <si>
-    <t>Glycine, serine, alanine and threonine metabolism</t>
-  </si>
-  <si>
-    <t>E710,E2344,E708,E2442,E2594</t>
-  </si>
-  <si>
-    <t>Pyrimidine metabolism</t>
-  </si>
-  <si>
-    <t>E1590,E1982,E1883</t>
-  </si>
-  <si>
-    <t>Ascorbate (Vitamin C) and Aldarate Metabolism</t>
-  </si>
-  <si>
-    <t>E1018,E712,E2342,E2174</t>
-  </si>
-  <si>
-    <t>Vitamin B3 (nicotinate and nicotinamide) metabolism</t>
-  </si>
-  <si>
-    <t>E1704</t>
-  </si>
-  <si>
-    <t>Methionine and cysteine metabolism</t>
-  </si>
-  <si>
-    <t>E1196</t>
-  </si>
-  <si>
-    <t>Purine metabolism</t>
-  </si>
-  <si>
-    <t>E1489,E513,E1808,E506</t>
-  </si>
-  <si>
-    <t>R Group Synthesis</t>
-  </si>
-  <si>
-    <t>C5-Branched dibasic acid metabolism</t>
-  </si>
-  <si>
-    <t>Pyruvate Metabolism</t>
-  </si>
-  <si>
-    <t>Chondroitin sulfate degradation</t>
-  </si>
-  <si>
-    <t>Di-unsaturated fatty acid beta-oxidation</t>
-  </si>
-  <si>
-    <t>Glycerolipid metabolism</t>
-  </si>
-  <si>
-    <t>Glycosylphosphatidylinositol(GPI)-anchor biosynthesis</t>
-  </si>
-  <si>
-    <t>Parathio degradation</t>
-  </si>
-  <si>
-    <t>Electron transport chain</t>
-  </si>
-  <si>
-    <t>Vitamin H (biotin) metabolism</t>
-  </si>
-  <si>
-    <t>Heparan sulfate biosynthesis</t>
-  </si>
-  <si>
-    <t>Glyoxylate and Dicarboxylate Metabolism</t>
-  </si>
-  <si>
-    <t>Glycosaminoglycan degradation</t>
-  </si>
-  <si>
-    <t>Fatty acid oxidation</t>
-  </si>
-  <si>
-    <t>ROS Detoxification</t>
-  </si>
-  <si>
-    <t>Mono-unsaturated fatty acid beta-oxidation</t>
-  </si>
-  <si>
-    <t>Geraniol degradation</t>
-  </si>
-  <si>
-    <t>Vitamin D</t>
-  </si>
-  <si>
-    <t>Dynorphin metabolism</t>
-  </si>
-  <si>
-    <t>Fatty acid oxidation, peroxisome</t>
-  </si>
-  <si>
-    <t>Polyunsaturated fatty acid biosynthesis</t>
-  </si>
-  <si>
-    <t>Alanine and Aspartate Metabolism</t>
-  </si>
-  <si>
-    <t>TCA cycle</t>
-  </si>
-  <si>
-    <t>3-Chloroacrylic acid degradation</t>
-  </si>
-  <si>
-    <t>Sphingolipid metabolism</t>
-  </si>
-  <si>
-    <t>Proteoglycan biosynthesis</t>
-  </si>
-  <si>
-    <t>Vitamin K metabolism</t>
-  </si>
-  <si>
-    <t>Glutamate metabolism</t>
-  </si>
-  <si>
-    <t>Benzoate degradation via CoA ligation</t>
-  </si>
-  <si>
-    <t>Dimethyl-branched-chain fatty acid mitochondrial beta-oxidation</t>
-  </si>
-  <si>
-    <t>Atrazine degradation</t>
-  </si>
-  <si>
-    <t>Vitamin B12 (cyanocobalamin) metabolism</t>
-  </si>
-  <si>
-    <t>Carbon fixation</t>
-  </si>
-  <si>
-    <t>Nucleotide Sugar Metabolism</t>
-  </si>
-  <si>
-    <t>1- and 2-Methylnaphthalene degradation</t>
-  </si>
-  <si>
-    <t>Nitrogen metabolism</t>
-  </si>
-  <si>
-    <t>Trihydroxycoprostanoyl-CoA beta-oxidation</t>
-  </si>
-  <si>
-    <t>Phytanic acid peroxisomal oxidation</t>
   </si>
   <si>
     <t>Selenoamino acid metabolism</t>
@@ -1228,13 +1075,13 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C2">
         <v>63</v>
       </c>
       <c r="D2">
-        <v>0.002604823124107218</v>
+        <v>0.001025192853901615</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1251,13 +1098,13 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D3">
-        <v>0.004117301067137215</v>
+        <v>0.0410245205962925</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1274,13 +1121,13 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C4">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="D4">
-        <v>0.02503991261238551</v>
+        <v>0.04413371203845314</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1300,10 +1147,10 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>0.05848248046382657</v>
+        <v>0.04621771062671216</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1320,13 +1167,13 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="D6">
-        <v>0.05848248046382657</v>
+        <v>0.04888993462294752</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1343,13 +1190,13 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>17</v>
       </c>
       <c r="D7">
-        <v>0.05873456012099824</v>
+        <v>0.05984773365153527</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1366,13 +1213,13 @@
         <v>31</v>
       </c>
       <c r="B8">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C8">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D8">
-        <v>0.06587681707419545</v>
+        <v>0.06248634476731484</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1389,13 +1236,13 @@
         <v>35</v>
       </c>
       <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9">
         <v>7</v>
       </c>
-      <c r="C9">
-        <v>13</v>
-      </c>
       <c r="D9">
-        <v>0.07226283505587766</v>
+        <v>0.07371304683954892</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1412,13 +1259,13 @@
         <v>39</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D10">
-        <v>0.08234602134274431</v>
+        <v>0.1371741651400817</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
@@ -1435,1639 +1282,1483 @@
         <v>43</v>
       </c>
       <c r="B11">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D11">
-        <v>0.08553903033358541</v>
+        <v>0.1436446446278214</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G11" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12">
+        <v>13</v>
+      </c>
+      <c r="D12">
+        <v>0.1459975462597267</v>
+      </c>
+      <c r="E12" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" t="s">
         <v>47</v>
       </c>
-      <c r="B12">
-        <v>5</v>
-      </c>
-      <c r="C12">
-        <v>9</v>
-      </c>
-      <c r="D12">
-        <v>0.09016049071506596</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>48</v>
-      </c>
-      <c r="F12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13">
+        <v>35</v>
+      </c>
+      <c r="D13">
+        <v>0.1676778541537117</v>
+      </c>
+      <c r="E13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" t="s">
         <v>51</v>
       </c>
-      <c r="B13">
-        <v>10</v>
-      </c>
-      <c r="C13">
-        <v>21</v>
-      </c>
-      <c r="D13">
-        <v>0.09663053524913873</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>52</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C14">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D14">
-        <v>0.09663053524913873</v>
+        <v>0.169240853094906</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="G14" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D15">
-        <v>0.09990757079237039</v>
+        <v>0.1726525604611687</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="G15" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16">
-        <v>0.09990757079237039</v>
+        <v>0.1756777197021899</v>
       </c>
       <c r="E16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="G16" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17">
-        <v>0.09990757079237039</v>
+        <v>0.1756777197021899</v>
       </c>
       <c r="E17" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="G17" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B18">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>130</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>0.1356188555583564</v>
+        <v>0.1756777197021899</v>
       </c>
       <c r="E18" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F18" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G18" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>0.1420048735400387</v>
+        <v>0.1756777197021899</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F19" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="G19" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D20">
-        <v>0.1536005377699353</v>
+        <v>0.1863498092469034</v>
       </c>
       <c r="E20" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F20" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G20" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D21">
-        <v>0.1536005377699353</v>
+        <v>0.2022823145829482</v>
       </c>
       <c r="E21" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F21" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="G21" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D22">
-        <v>0.1536005377699353</v>
+        <v>0.2172904657064587</v>
       </c>
       <c r="E22" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="G22" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B23">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>172</v>
+        <v>7</v>
       </c>
       <c r="D23">
-        <v>0.1924208049743719</v>
+        <v>0.2172904657064587</v>
       </c>
       <c r="E23" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F23" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="G23" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24">
         <v>7</v>
       </c>
-      <c r="C24">
-        <v>17</v>
-      </c>
       <c r="D24">
-        <v>0.2395597008654735</v>
+        <v>0.2172904657064587</v>
       </c>
       <c r="E24" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="F24" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="G24" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="B25">
         <v>5</v>
       </c>
       <c r="C25">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D25">
-        <v>0.2484665154188724</v>
+        <v>0.2357607435169157</v>
       </c>
       <c r="E25" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="F25" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="B26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C26">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D26">
-        <v>0.2484665154188724</v>
+        <v>0.2359792272398783</v>
       </c>
       <c r="E26" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="F26" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="G26" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="B27">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C27">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D27">
-        <v>0.2609864717250651</v>
+        <v>0.2363153560444362</v>
       </c>
       <c r="E27" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="F27" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G27" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="B28">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C28">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D28">
-        <v>0.2609864717250651</v>
+        <v>0.2363153560444362</v>
       </c>
       <c r="E28" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="F28" t="s">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="G28" t="s">
-        <v>103</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
         <v>3</v>
       </c>
-      <c r="C29">
-        <v>7</v>
-      </c>
       <c r="D29">
-        <v>0.261574657591799</v>
+        <v>0.2390548058015832</v>
       </c>
       <c r="E29" t="s">
-        <v>105</v>
-      </c>
-      <c r="F29" t="s">
-        <v>106</v>
-      </c>
-      <c r="G29" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
         <v>3</v>
       </c>
-      <c r="C30">
-        <v>7</v>
-      </c>
       <c r="D30">
-        <v>0.261574657591799</v>
+        <v>0.2390548058015832</v>
       </c>
       <c r="E30" t="s">
-        <v>109</v>
-      </c>
-      <c r="F30" t="s">
-        <v>110</v>
-      </c>
-      <c r="G30" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="B31">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D31">
-        <v>0.2727501890597429</v>
+        <v>0.2390548058015832</v>
       </c>
       <c r="E31" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="F31" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="G31" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="B32">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C32">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D32">
-        <v>0.2784639946223006</v>
+        <v>0.2459286398547924</v>
       </c>
       <c r="E32" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="F32" t="s">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="G32" t="s">
-        <v>119</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="B33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D33">
-        <v>0.2955213847575834</v>
+        <v>0.248399186568293</v>
       </c>
       <c r="E33" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="F33" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="G33" t="s">
-        <v>123</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="B34">
+        <v>4</v>
+      </c>
+      <c r="C34">
         <v>17</v>
       </c>
-      <c r="C34">
-        <v>46</v>
-      </c>
       <c r="D34">
-        <v>0.3118225359213512</v>
+        <v>0.248399186568293</v>
       </c>
       <c r="E34" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="F34" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="G34" t="s">
-        <v>127</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="B35">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="D35">
-        <v>0.3118225359213512</v>
+        <v>0.2573570192097612</v>
       </c>
       <c r="E35" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="F35" t="s">
-        <v>130</v>
+        <v>59</v>
       </c>
       <c r="G35" t="s">
-        <v>131</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C36">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="D36">
-        <v>0.3188807663221578</v>
+        <v>0.2803986487622057</v>
       </c>
       <c r="E36" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="F36" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="G36" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C37">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D37">
-        <v>0.3282077136375094</v>
+        <v>0.3039948908421707</v>
       </c>
       <c r="E37" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="F37" t="s">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s">
-        <v>139</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D38">
-        <v>0.3376186875052516</v>
+        <v>0.3234567486260735</v>
       </c>
       <c r="E38" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="F38" t="s">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="G38" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="B39">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D39">
-        <v>0.3861020082346021</v>
+        <v>0.3263474563452715</v>
       </c>
       <c r="E39" t="s">
-        <v>145</v>
-      </c>
-      <c r="F39" t="s">
-        <v>146</v>
-      </c>
-      <c r="G39" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="B40">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C40">
+        <v>19</v>
+      </c>
+      <c r="D40">
+        <v>0.3363640947210971</v>
+      </c>
+      <c r="E40" t="s">
+        <v>118</v>
+      </c>
+      <c r="F40" t="s">
+        <v>47</v>
+      </c>
+      <c r="G40" t="s">
         <v>48</v>
-      </c>
-      <c r="D40">
-        <v>0.3866061675489454</v>
-      </c>
-      <c r="E40" t="s">
-        <v>149</v>
-      </c>
-      <c r="F40" t="s">
-        <v>126</v>
-      </c>
-      <c r="G40" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="B41">
         <v>3</v>
       </c>
       <c r="C41">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D41">
-        <v>0.4129064784471893</v>
+        <v>0.3625653350363859</v>
       </c>
       <c r="E41" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="F41" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="G41" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="B42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D42">
-        <v>0.4143349298378288</v>
+        <v>0.3625653350363859</v>
       </c>
       <c r="E42" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="F42" t="s">
-        <v>154</v>
+        <v>37</v>
       </c>
       <c r="G42" t="s">
-        <v>155</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="B43">
         <v>2</v>
       </c>
       <c r="C43">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D43">
-        <v>0.416939752961936</v>
+        <v>0.3655232685164955</v>
       </c>
       <c r="E43" t="s">
-        <v>157</v>
+        <v>124</v>
       </c>
       <c r="F43" t="s">
-        <v>158</v>
+        <v>59</v>
       </c>
       <c r="G43" t="s">
-        <v>159</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="B44">
         <v>2</v>
       </c>
       <c r="C44">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D44">
-        <v>0.416939752961936</v>
+        <v>0.3655232685164955</v>
       </c>
       <c r="E44" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="F44" t="s">
-        <v>134</v>
+        <v>59</v>
       </c>
       <c r="G44" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="B45">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C45">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="D45">
-        <v>0.4287874968490043</v>
+        <v>0.3829011277121393</v>
       </c>
       <c r="E45" t="s">
-        <v>163</v>
-      </c>
-      <c r="F45" t="s">
-        <v>164</v>
-      </c>
-      <c r="G45" t="s">
-        <v>165</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C46">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D46">
-        <v>0.434333249306781</v>
+        <v>0.3900942841296785</v>
       </c>
       <c r="E46" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="F46" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="G46" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D47">
-        <v>0.434333249306781</v>
+        <v>0.4009680509571268</v>
       </c>
       <c r="E47" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="F47" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="G47" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D48">
-        <v>0.434333249306781</v>
+        <v>0.4424463454395725</v>
       </c>
       <c r="E48" t="s">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="F48" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="G48" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D49">
-        <v>0.434333249306781</v>
+        <v>0.4588158182215425</v>
       </c>
       <c r="E49" t="s">
-        <v>170</v>
+        <v>136</v>
+      </c>
+      <c r="F49" t="s">
+        <v>59</v>
+      </c>
+      <c r="G49" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
       <c r="C50">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D50">
-        <v>0.434333249306781</v>
+        <v>0.4633535570830742</v>
       </c>
       <c r="E50" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="B51">
         <v>1</v>
       </c>
       <c r="C51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D51">
-        <v>0.434333249306781</v>
+        <v>0.4633535570830742</v>
       </c>
       <c r="E51" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="B52">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C52">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D52">
-        <v>0.4523149315183598</v>
+        <v>0.4633535570830742</v>
       </c>
       <c r="E52" t="s">
-        <v>176</v>
-      </c>
-      <c r="F52" t="s">
-        <v>41</v>
-      </c>
-      <c r="G52" t="s">
-        <v>42</v>
+        <v>142</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="B53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D53">
-        <v>0.4532392235946559</v>
+        <v>0.4633535570830742</v>
       </c>
       <c r="E53" t="s">
-        <v>178</v>
-      </c>
-      <c r="F53" t="s">
-        <v>179</v>
-      </c>
-      <c r="G53" t="s">
-        <v>180</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="B54">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D54">
-        <v>0.4532392235946559</v>
+        <v>0.4633535570830742</v>
       </c>
       <c r="E54" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="F54" t="s">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="G54" t="s">
-        <v>22</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>183</v>
+        <v>149</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D55">
-        <v>0.4576926308713554</v>
+        <v>0.4995546293339608</v>
       </c>
       <c r="E55" t="s">
-        <v>184</v>
-      </c>
-      <c r="F55" t="s">
-        <v>138</v>
-      </c>
-      <c r="G55" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>185</v>
+        <v>151</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D56">
-        <v>0.4710528527014536</v>
+        <v>0.5601250399152955</v>
       </c>
       <c r="E56" t="s">
-        <v>186</v>
-      </c>
-      <c r="F56" t="s">
-        <v>134</v>
-      </c>
-      <c r="G56" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="D57">
-        <v>0.4710528527014536</v>
+        <v>0.5607972975244113</v>
       </c>
       <c r="E57" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="F57" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="G57" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D58">
-        <v>0.4710528527014536</v>
+        <v>0.5734525470160166</v>
       </c>
       <c r="E58" t="s">
-        <v>157</v>
-      </c>
-      <c r="F58" t="s">
-        <v>158</v>
-      </c>
-      <c r="G58" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D59">
-        <v>0.4710528527014536</v>
+        <v>0.5734525470160166</v>
       </c>
       <c r="E59" t="s">
-        <v>191</v>
-      </c>
-      <c r="F59" t="s">
-        <v>192</v>
-      </c>
-      <c r="G59" t="s">
-        <v>193</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="B60">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D60">
-        <v>0.5034871019242081</v>
+        <v>0.5734525470160166</v>
       </c>
       <c r="E60" t="s">
-        <v>195</v>
-      </c>
-      <c r="F60" t="s">
-        <v>146</v>
-      </c>
-      <c r="G60" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>196</v>
+        <v>162</v>
       </c>
       <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61">
         <v>11</v>
       </c>
-      <c r="C61">
-        <v>35</v>
-      </c>
       <c r="D61">
-        <v>0.5132341820015125</v>
+        <v>0.5734525470160166</v>
       </c>
       <c r="E61" t="s">
-        <v>197</v>
-      </c>
-      <c r="F61" t="s">
-        <v>198</v>
-      </c>
-      <c r="G61" t="s">
-        <v>199</v>
+        <v>163</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>200</v>
+        <v>164</v>
       </c>
       <c r="B62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D62">
-        <v>0.5173514830686496</v>
+        <v>0.5827633149022705</v>
       </c>
       <c r="E62" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="F62" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="G62" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D63">
-        <v>0.5291152004033275</v>
+        <v>0.586880892758105</v>
       </c>
       <c r="E63" t="s">
-        <v>203</v>
+        <v>142</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>204</v>
+        <v>167</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C64">
-        <v>4</v>
+        <v>130</v>
       </c>
       <c r="D64">
-        <v>0.5291152004033275</v>
+        <v>0.5978554982269205</v>
       </c>
       <c r="E64" t="s">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="F64" t="s">
-        <v>75</v>
+        <v>169</v>
       </c>
       <c r="G64" t="s">
-        <v>76</v>
+        <v>170</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>205</v>
+        <v>171</v>
       </c>
       <c r="B65">
         <v>1</v>
       </c>
       <c r="C65">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D65">
-        <v>0.5291152004033275</v>
+        <v>0.599872271054268</v>
       </c>
       <c r="E65" t="s">
-        <v>206</v>
+        <v>172</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="B66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D66">
-        <v>0.5304596252415763</v>
+        <v>0.6220063528344062</v>
       </c>
       <c r="E66" t="s">
-        <v>208</v>
+        <v>174</v>
       </c>
       <c r="F66" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="G66" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>209</v>
+        <v>175</v>
       </c>
       <c r="B67">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C67">
-        <v>18</v>
+        <v>172</v>
       </c>
       <c r="D67">
-        <v>0.5489454667674986</v>
+        <v>0.6362246012672056</v>
       </c>
       <c r="E67" t="s">
-        <v>210</v>
+        <v>176</v>
       </c>
       <c r="F67" t="s">
-        <v>211</v>
+        <v>177</v>
       </c>
       <c r="G67" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>213</v>
+        <v>179</v>
       </c>
       <c r="B68">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C68">
         <v>19</v>
       </c>
       <c r="D68">
-        <v>0.5876817074195446</v>
+        <v>0.6393001798289104</v>
       </c>
       <c r="E68" t="s">
-        <v>214</v>
-      </c>
-      <c r="F68" t="s">
-        <v>215</v>
-      </c>
-      <c r="G68" t="s">
-        <v>216</v>
+        <v>163</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>217</v>
+        <v>180</v>
       </c>
       <c r="B69">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C69">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D69">
-        <v>0.5876817074195446</v>
+        <v>0.6439891766524932</v>
       </c>
       <c r="E69" t="s">
-        <v>218</v>
+        <v>181</v>
       </c>
       <c r="F69" t="s">
-        <v>219</v>
+        <v>37</v>
       </c>
       <c r="G69" t="s">
-        <v>220</v>
+        <v>38</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>221</v>
+        <v>182</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C70">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D70">
-        <v>0.5915469288295101</v>
-      </c>
-      <c r="E70" t="s">
-        <v>222</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>223</v>
+        <v>183</v>
       </c>
       <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
         <v>2</v>
       </c>
-      <c r="C71">
-        <v>9</v>
-      </c>
       <c r="D71">
-        <v>0.598941265439879</v>
-      </c>
-      <c r="E71" t="s">
-        <v>224</v>
-      </c>
-      <c r="F71" t="s">
-        <v>134</v>
-      </c>
-      <c r="G71" t="s">
-        <v>135</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>225</v>
+        <v>184</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C72">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D72">
-        <v>0.6524661793126628</v>
-      </c>
-      <c r="E72" t="s">
-        <v>226</v>
-      </c>
-      <c r="F72" t="s">
-        <v>134</v>
-      </c>
-      <c r="G72" t="s">
-        <v>135</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>227</v>
+        <v>185</v>
       </c>
       <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
         <v>2</v>
       </c>
-      <c r="C73">
-        <v>11</v>
-      </c>
       <c r="D73">
-        <v>0.6524661793126628</v>
-      </c>
-      <c r="E73" t="s">
-        <v>228</v>
-      </c>
-      <c r="F73" t="s">
-        <v>134</v>
-      </c>
-      <c r="G73" t="s">
-        <v>135</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>229</v>
+        <v>186</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C74">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D74">
-        <v>0.6524661793126628</v>
-      </c>
-      <c r="E74" t="s">
-        <v>230</v>
-      </c>
-      <c r="F74" t="s">
-        <v>134</v>
-      </c>
-      <c r="G74" t="s">
-        <v>135</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>231</v>
+        <v>187</v>
       </c>
       <c r="B75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D75">
-        <v>0.6579279052180489</v>
-      </c>
-      <c r="E75" t="s">
-        <v>232</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="B76">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C76">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>0.6680110915049156</v>
-      </c>
-      <c r="E76" t="s">
-        <v>234</v>
-      </c>
-      <c r="F76" t="s">
-        <v>215</v>
-      </c>
-      <c r="G76" t="s">
-        <v>216</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>235</v>
+        <v>189</v>
       </c>
       <c r="B77">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C77">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D77">
-        <v>0.6871691454499622</v>
-      </c>
-      <c r="E77" t="s">
-        <v>236</v>
-      </c>
-      <c r="F77" t="s">
-        <v>110</v>
-      </c>
-      <c r="G77" t="s">
-        <v>111</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>237</v>
+        <v>190</v>
       </c>
       <c r="B78">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C78">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>0.6904461809931939</v>
-      </c>
-      <c r="E78" t="s">
-        <v>238</v>
-      </c>
-      <c r="F78" t="s">
-        <v>21</v>
-      </c>
-      <c r="G78" t="s">
-        <v>22</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>239</v>
+        <v>191</v>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C79">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D79">
-        <v>0.7072514914713049</v>
-      </c>
-      <c r="E79" t="s">
-        <v>240</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>241</v>
+        <v>192</v>
       </c>
       <c r="B80">
+        <v>0</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80">
+        <v>0.6490143022806339</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
+        <v>193</v>
+      </c>
+      <c r="B81">
+        <v>0</v>
+      </c>
+      <c r="C81">
+        <v>3</v>
+      </c>
+      <c r="D81">
+        <v>0.6490143022806339</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
+        <v>194</v>
+      </c>
+      <c r="B82">
+        <v>0</v>
+      </c>
+      <c r="C82">
+        <v>3</v>
+      </c>
+      <c r="D82">
+        <v>0.6490143022806339</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" t="s">
+        <v>195</v>
+      </c>
+      <c r="B83">
+        <v>0</v>
+      </c>
+      <c r="C83">
+        <v>5</v>
+      </c>
+      <c r="D83">
+        <v>0.6490143022806339</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" t="s">
+        <v>196</v>
+      </c>
+      <c r="B84">
+        <v>0</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <v>0.6490143022806339</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" t="s">
+        <v>197</v>
+      </c>
+      <c r="B85">
+        <v>0</v>
+      </c>
+      <c r="C85">
         <v>1</v>
       </c>
-      <c r="C80">
-        <v>19</v>
-      </c>
-      <c r="D80">
-        <v>0.7254012267876649</v>
-      </c>
-      <c r="E80" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
-      <c r="A81" t="s">
-        <v>243</v>
-      </c>
-      <c r="B81">
-        <v>4</v>
-      </c>
-      <c r="C81">
-        <v>39</v>
-      </c>
-      <c r="D81">
-        <v>0.7257373329972271</v>
-      </c>
-      <c r="E81" t="s">
-        <v>244</v>
-      </c>
-      <c r="F81" t="s">
-        <v>21</v>
-      </c>
-      <c r="G81" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
-      <c r="A82" t="s">
-        <v>245</v>
-      </c>
-      <c r="B82">
-        <v>0</v>
-      </c>
-      <c r="C82">
-        <v>0</v>
-      </c>
-      <c r="D82">
-        <v>0.7258213595496177</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
-      <c r="A83" t="s">
-        <v>246</v>
-      </c>
-      <c r="B83">
-        <v>0</v>
-      </c>
-      <c r="C83">
-        <v>2</v>
-      </c>
-      <c r="D83">
-        <v>0.7258213595496177</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
-      <c r="A84" t="s">
-        <v>247</v>
-      </c>
-      <c r="B84">
-        <v>0</v>
-      </c>
-      <c r="C84">
-        <v>1</v>
-      </c>
-      <c r="D84">
-        <v>0.7258213595496177</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
-      <c r="A85" t="s">
-        <v>248</v>
-      </c>
-      <c r="B85">
-        <v>0</v>
-      </c>
-      <c r="C85">
-        <v>2</v>
-      </c>
       <c r="D85">
-        <v>0.7258213595496177</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7">
+        <v>0.6490143022806339</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>249</v>
+        <v>198</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -3076,26 +2767,26 @@
         <v>4</v>
       </c>
       <c r="D86">
-        <v>0.7258213595496177</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7">
+        <v>0.6490143022806339</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>250</v>
+        <v>199</v>
       </c>
       <c r="B87">
         <v>0</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D87">
-        <v>0.7258213595496177</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7">
+        <v>0.6490143022806339</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>251</v>
+        <v>200</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -3104,82 +2795,82 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>0.7258213595496177</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7">
+        <v>0.6490143022806339</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>252</v>
+        <v>201</v>
       </c>
       <c r="B89">
         <v>0</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D89">
-        <v>0.7258213595496177</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7">
+        <v>0.6490143022806339</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>253</v>
+        <v>202</v>
       </c>
       <c r="B90">
         <v>0</v>
       </c>
       <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <v>0.6490143022806339</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" t="s">
+        <v>203</v>
+      </c>
+      <c r="B91">
+        <v>0</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="D91">
+        <v>0.6490143022806339</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" t="s">
+        <v>204</v>
+      </c>
+      <c r="B92">
+        <v>0</v>
+      </c>
+      <c r="C92">
+        <v>2</v>
+      </c>
+      <c r="D92">
+        <v>0.6490143022806339</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" t="s">
+        <v>205</v>
+      </c>
+      <c r="B93">
+        <v>0</v>
+      </c>
+      <c r="C93">
         <v>3</v>
       </c>
-      <c r="D90">
-        <v>0.7258213595496177</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7">
-      <c r="A91" t="s">
-        <v>254</v>
-      </c>
-      <c r="B91">
-        <v>0</v>
-      </c>
-      <c r="C91">
-        <v>5</v>
-      </c>
-      <c r="D91">
-        <v>0.7258213595496177</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
-      <c r="A92" t="s">
-        <v>255</v>
-      </c>
-      <c r="B92">
-        <v>0</v>
-      </c>
-      <c r="C92">
-        <v>0</v>
-      </c>
-      <c r="D92">
-        <v>0.7258213595496177</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
-      <c r="A93" t="s">
-        <v>256</v>
-      </c>
-      <c r="B93">
-        <v>0</v>
-      </c>
-      <c r="C93">
-        <v>1</v>
-      </c>
       <c r="D93">
-        <v>0.7258213595496177</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
+        <v>0.6490143022806339</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>257</v>
+        <v>206</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -3188,26 +2879,26 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>0.7258213595496177</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
+        <v>0.6490143022806339</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>258</v>
+        <v>207</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
       <c r="C95">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>0.7258213595496177</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
+        <v>0.6490143022806339</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>259</v>
+        <v>208</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -3216,26 +2907,26 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>260</v>
+        <v>209</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
       <c r="C97">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -3244,54 +2935,54 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>262</v>
+        <v>211</v>
       </c>
       <c r="B99">
         <v>0</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D99">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>263</v>
+        <v>212</v>
       </c>
       <c r="B100">
         <v>0</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D100">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>264</v>
+        <v>213</v>
       </c>
       <c r="B101">
         <v>0</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D101">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>265</v>
+        <v>214</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -3300,40 +2991,40 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>266</v>
+        <v>215</v>
       </c>
       <c r="B103">
         <v>0</v>
       </c>
       <c r="C103">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D103">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>267</v>
+        <v>216</v>
       </c>
       <c r="B104">
         <v>0</v>
       </c>
       <c r="C104">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D104">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -3342,68 +3033,68 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>269</v>
+        <v>218</v>
       </c>
       <c r="B106">
         <v>0</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D106">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>270</v>
+        <v>219</v>
       </c>
       <c r="B107">
         <v>0</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D107">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>271</v>
+        <v>220</v>
       </c>
       <c r="B108">
         <v>0</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>272</v>
+        <v>221</v>
       </c>
       <c r="B109">
         <v>0</v>
       </c>
       <c r="C109">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>273</v>
+        <v>222</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -3412,26 +3103,26 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>274</v>
+        <v>223</v>
       </c>
       <c r="B111">
         <v>0</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D111">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>275</v>
+        <v>224</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -3440,26 +3131,26 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>276</v>
+        <v>225</v>
       </c>
       <c r="B113">
         <v>0</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -3468,26 +3159,26 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
       <c r="B115">
         <v>0</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D115">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>279</v>
+        <v>228</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -3496,12 +3187,12 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>280</v>
+        <v>229</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -3510,40 +3201,40 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>281</v>
+        <v>230</v>
       </c>
       <c r="B118">
         <v>0</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D118">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>282</v>
+        <v>231</v>
       </c>
       <c r="B119">
         <v>0</v>
       </c>
       <c r="C119">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D119">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>283</v>
+        <v>232</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3552,7 +3243,7 @@
         <v>4</v>
       </c>
       <c r="D120">
-        <v>0.7258213595496177</v>
+        <v>0.6490143022806339</v>
       </c>
     </row>
   </sheetData>
